--- a/files/九龙-九龙塘-博峰.xlsx
+++ b/files/九龙-九龙塘-博峰.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="住宅大楼 - 东翼 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="住宅大楼 - 西翼 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,65 +39,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -110,42 +51,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -175,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -188,42 +93,6 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -590,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -608,7 +477,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>博峯 - 一手销控汇总明细</t>
+          <t>博峰 - 一手销控汇总明细</t>
         </is>
       </c>
     </row>
@@ -2859,6 +2728,106 @@
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>1号屋</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>2623</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2号屋</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>2621</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2871,750 +2840,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>博峯 - 住宅大楼 - 东翼 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>22 套</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>22 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>A | 2217呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>A | 2207呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>博峯 - 住宅大楼 - 西翼 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>22 套</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>22 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>A | 2217呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>A | 2207呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>A | 1322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>B | 1089呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-九龙塘-博峰.xlsx
+++ b/files/九龙-九龙塘-博峰.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="住宅大楼 - 东翼" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="住宅大楼 - 西翼" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +42,115 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +161,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,6 +238,69 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2840,4 +3049,886 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 东翼 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>A | 2217呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>A | 2207呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>住宅大楼 - 西翼 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>A | 2217呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>A | 2207呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>A | 1322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>B | 1089呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>博峰 - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1号屋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2号屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>1号屋
+2623呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>2号屋
+2621呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-九龙塘-博峰.xlsx
+++ b/files/九龙-九龙塘-博峰.xlsx
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -681,6 +681,10 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -738,6 +742,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -788,6 +812,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -838,6 +882,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -888,6 +952,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -938,6 +1022,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -988,6 +1092,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1038,6 +1162,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1088,6 +1232,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1138,6 +1302,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1188,6 +1372,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1238,6 +1442,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1288,6 +1512,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1338,6 +1582,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1388,6 +1652,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1438,6 +1722,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1488,6 +1792,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1538,6 +1862,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1588,6 +1932,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1638,6 +2002,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1688,6 +2072,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1738,6 +2142,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1788,6 +2212,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1838,6 +2282,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1888,6 +2352,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1938,6 +2422,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1988,6 +2492,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2038,6 +2562,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2088,6 +2632,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2138,6 +2702,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2188,6 +2772,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2238,6 +2842,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2288,6 +2912,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2338,6 +2982,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2388,6 +3052,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2438,6 +3122,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2488,6 +3192,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2538,6 +3262,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2588,6 +3332,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2638,6 +3402,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2688,6 +3472,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2738,6 +3542,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2788,6 +3612,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2838,6 +3682,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2888,6 +3752,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2938,6 +3822,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2988,6 +3892,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3038,13 +3962,33 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
